--- a/app/reports/FLR_research.xlsx
+++ b/app/reports/FLR_research.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -151,6 +151,8 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -593,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -618,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-05-31 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-01 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -638,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.769</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -654,7 +656,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -687,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>45.76</v>
+        <v>46.62</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -728,56 +730,71 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.769</v>
+        <v>0.754</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>comps_percentile</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Peer-relative ranking of P/E, EV/EBITDA, EV/Rev</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Honest caveats (read before acting)</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
-        </is>
-      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
+          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
+          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
+          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>This is a SIGNAL screen, not an investment thesis. Verify with primary filings before acting.</t>
         </is>
@@ -788,6 +805,7 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A1:C2"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
@@ -795,7 +813,6 @@
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -862,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.0445300006866455</v>
+        <v>0.0447700023651123</v>
       </c>
     </row>
     <row r="6">
@@ -1191,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>139669885.3146853</v>
+        <v>139669887.9450879</v>
       </c>
     </row>
     <row r="36">
@@ -1212,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>45.76</v>
+        <v>46.62</v>
       </c>
     </row>
     <row r="38">
@@ -1417,7 +1434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1491,10 +1508,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>6391293952</v>
+        <v>6511410176</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>20.89</v>
+        <v>21.29</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>-10.96</v>
@@ -1503,56 +1520,250 @@
         <v>0.26</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ACM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="n">
+        <v>9291628544</v>
+      </c>
+      <c r="D6" s="33" t="n">
+        <v>15.093007</v>
+      </c>
+      <c r="E6" s="33" t="n">
+        <v>8.946</v>
+      </c>
+      <c r="F6" s="33" t="n">
+        <v>0.715</v>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BLD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TopBuild Corp.</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="n">
+        <v>11641567232</v>
+      </c>
+      <c r="D7" s="33" t="n">
+        <v>23.26603</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>14.274</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EME</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EMCOR Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="n">
+        <v>37043081216</v>
+      </c>
+      <c r="D8" s="33" t="n">
+        <v>27.941551</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <v>19.637</v>
+      </c>
+      <c r="F8" s="33" t="n">
+        <v>2.048</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GLDD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Great Lakes Dredge &amp; Dock Corpo</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="n">
+        <v>1135273600</v>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>15.74074</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <v>9.353</v>
+      </c>
+      <c r="F9" s="33" t="n">
+        <v>1.779</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Granite Construction Incorporat</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n">
+        <v>5945176064</v>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>37.029972</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <v>15.371</v>
+      </c>
+      <c r="F10" s="33" t="n">
+        <v>1.507</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jacobs Solutions Inc.</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n">
+        <v>14625498112</v>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>36.536873</v>
+      </c>
+      <c r="E11" s="33" t="n">
+        <v>16.908</v>
+      </c>
+      <c r="F11" s="33" t="n">
+        <v>1.315</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KBR, Inc.</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n">
+        <v>4558098944</v>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>10.60472</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <v>10.482</v>
+      </c>
+      <c r="F12" s="33" t="n">
+        <v>0.891</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MTRX</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Matrix Service Company</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n">
+        <v>364896032</v>
+      </c>
+      <c r="D13" s="33" t="n"/>
+      <c r="E13" s="33" t="n">
+        <v>-62.731</v>
+      </c>
+      <c r="F13" s="33" t="n">
+        <v>0.183</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Peer median</t>
         </is>
       </c>
-      <c r="D7" s="32">
-        <f>MEDIAN(D6:D5)</f>
-        <v/>
-      </c>
-      <c r="E7" s="32">
-        <f>MEDIAN(E6:E5)</f>
-        <v/>
-      </c>
-      <c r="F7" s="32">
-        <f>MEDIAN(F6:F5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="D15" s="34">
+        <f>MEDIAN(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E15" s="34">
+        <f>MEDIAN(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F15" s="34">
+        <f>MEDIAN(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Peer mean</t>
         </is>
       </c>
-      <c r="D8" s="32">
-        <f>AVERAGE(D6:D5)</f>
-        <v/>
-      </c>
-      <c r="E8" s="32">
-        <f>AVERAGE(E6:E5)</f>
-        <v/>
-      </c>
-      <c r="F8" s="32">
-        <f>AVERAGE(F6:F5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="D16" s="34">
+        <f>AVERAGE(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E16" s="34">
+        <f>AVERAGE(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F16" s="34">
+        <f>AVERAGE(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Target percentile vs peers</t>
         </is>
       </c>
-      <c r="D9" s="33" t="n"/>
-      <c r="E9" s="33" t="n"/>
-      <c r="F9" s="33" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="D17" s="35" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>(higher pct = more expensive than peers)</t>
         </is>

--- a/app/reports/FLR_research.xlsx
+++ b/app/reports/FLR_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-01 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-02 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.793</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>46.62</v>
+        <v>49.06</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.754</v>
+        <v>0.713</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.0447700023651123</v>
+        <v>0.04456999778747558</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>139669887.9450879</v>
+        <v>139669895.1487974</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>46.62</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="38">
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>6511410176</v>
+        <v>6852205056</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>21.29</v>
+        <v>22.4</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>-10.96</v>
+        <v>-11.27</v>
       </c>
       <c r="F5" s="31" t="n">
         <v>0.26</v>
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>9291628544</v>
+        <v>8893786112</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>15.093007</v>
+        <v>14.446764</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>8.946</v>
+        <v>9.236000000000001</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.715</v>
+        <v>0.738</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>11641567232</v>
+        <v>11440764928</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>23.26603</v>
+        <v>22.875633</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>14.274</v>
+        <v>14.128</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>2.59</v>
+        <v>2.564</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>37043081216</v>
+        <v>36915494912</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>27.941551</v>
+        <v>27.864035</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>19.637</v>
+        <v>19.736</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.048</v>
+        <v>2.058</v>
       </c>
     </row>
     <row r="9">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>5945176064</v>
+        <v>5995266560</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>37.029972</v>
+        <v>37.34196</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>15.371</v>
+        <v>15.341</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>1.507</v>
+        <v>1.504</v>
       </c>
     </row>
     <row r="11">
@@ -1652,16 +1652,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>14625498112</v>
+        <v>14335019008</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>36.536873</v>
+        <v>35.705883</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>16.908</v>
+        <v>17.272</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.315</v>
+        <v>1.344</v>
       </c>
     </row>
     <row r="12">
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>4558098944</v>
+        <v>4506115072</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>10.60472</v>
+        <v>10.483776</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>10.482</v>
+        <v>10.618</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.891</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="13">
@@ -1700,14 +1700,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>364896032</v>
+        <v>386277760</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-62.731</v>
+        <v>-65.69</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.183</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/FLR_research.xlsx
+++ b/app/reports/FLR_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-02 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-03 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.793</v>
+        <v>0.788</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>49.06</v>
+        <v>49.95</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.713</v>
+        <v>0.698</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04456999778747558</v>
+        <v>0.04497000217437744</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>139669895.1487974</v>
+        <v>139669889.4094094</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>49.06</v>
+        <v>49.95</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>6852205056</v>
+        <v>6976510976</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>22.4</v>
+        <v>22.81</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>-11.27</v>
+        <v>-12.38</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>8893786112</v>
+        <v>9323053056</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>14.446764</v>
+        <v>15.144051</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>9.236000000000001</v>
+        <v>9.154</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.738</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>11440764928</v>
+        <v>11459058688</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>22.875633</v>
+        <v>22.886452</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>14.128</v>
+        <v>13.988</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>2.564</v>
+        <v>2.538</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>36915494912</v>
+        <v>37450108928</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>27.864035</v>
+        <v>28.239086</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>19.736</v>
+        <v>19.648</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.058</v>
+        <v>2.049</v>
       </c>
     </row>
     <row r="9">
@@ -1628,16 +1628,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>5995266560</v>
+        <v>6039232000</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>37.34196</v>
+        <v>37.71858</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>15.341</v>
+        <v>15.362</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>1.504</v>
+        <v>1.506</v>
       </c>
     </row>
     <row r="11">
@@ -1652,16 +1652,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>14335019008</v>
+        <v>14401733632</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>35.705883</v>
+        <v>35.977875</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>17.272</v>
+        <v>17.147</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.344</v>
+        <v>1.334</v>
       </c>
     </row>
     <row r="12">
@@ -1676,16 +1676,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>4506115072</v>
+        <v>4493435904</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>10.483776</v>
+        <v>10.454276</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>10.618</v>
+        <v>10.631</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.903</v>
+        <v>0.904</v>
       </c>
     </row>
     <row r="13">
@@ -1700,14 +1700,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>386277760</v>
+        <v>384589728</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-65.69</v>
+        <v>-69.218</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.192</v>
+        <v>0.202</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/FLR_research.xlsx
+++ b/app/reports/FLR_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-03 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-04 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.788</v>
+        <v>0.832</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>49.95</v>
+        <v>50.15</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.698</v>
+        <v>0.695</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>0.833</v>
+        <v>0.9</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04497000217437744</v>
+        <v>0.04470999717712403</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>139669889.4094094</v>
+        <v>139669893.998006</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>49.95</v>
+        <v>50.15</v>
       </c>
     </row>
     <row r="38">
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>6976510976</v>
+        <v>7004445184</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>22.81</v>
+        <v>22.9</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>-12.38</v>
+        <v>-12.7</v>
       </c>
       <c r="F5" s="31" t="n">
         <v>0.29</v>
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>9323053056</v>
+        <v>9279354880</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>15.144051</v>
+        <v>15.073069</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>9.154</v>
+        <v>9.252000000000001</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.731</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>11459058688</v>
+        <v>11476227072</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>22.886452</v>
+        <v>22.946539</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>13.988</v>
+        <v>14.027</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>2.538</v>
+        <v>2.545</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>37450108928</v>
+        <v>37392662528</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>28.239086</v>
+        <v>28.176846</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>19.648</v>
+        <v>19.943</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.049</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="9">
@@ -1600,21 +1600,13 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Great Lakes Dredge &amp; Dock Corpo</t>
-        </is>
-      </c>
-      <c r="C9" s="32" t="n">
-        <v>1135273600</v>
-      </c>
-      <c r="D9" s="33" t="n">
-        <v>15.74074</v>
-      </c>
-      <c r="E9" s="33" t="n">
-        <v>9.353</v>
-      </c>
-      <c r="F9" s="33" t="n">
-        <v>1.779</v>
-      </c>
+          <t>GLDD</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="n"/>
+      <c r="D9" s="33" t="n"/>
+      <c r="E9" s="33" t="n"/>
+      <c r="F9" s="33" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1628,16 +1620,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>6039232000</v>
+        <v>6179658752</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>37.71858</v>
+        <v>38.49046</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>15.362</v>
+        <v>15.581</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>1.506</v>
+        <v>1.528</v>
       </c>
     </row>
     <row r="11">
@@ -1652,16 +1644,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>14401733632</v>
+        <v>14564094976</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>35.977875</v>
+        <v>36.27647</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>17.147</v>
+        <v>17.071</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.334</v>
+        <v>1.328</v>
       </c>
     </row>
     <row r="12">
@@ -1676,13 +1668,13 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>4493435904</v>
+        <v>4566974464</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>10.454276</v>
+        <v>10.625368</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>10.631</v>
+        <v>10.633</v>
       </c>
       <c r="F12" s="33" t="n">
         <v>0.904</v>
@@ -1700,14 +1692,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>384589728</v>
+        <v>390779200</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-69.218</v>
+        <v>-70.47</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.202</v>
+        <v>0.206</v>
       </c>
     </row>
     <row r="15">
@@ -1755,7 +1747,7 @@
         </is>
       </c>
       <c r="D17" s="35" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="E17" s="35" t="n"/>
       <c r="F17" s="35" t="n">

--- a/app/reports/FLR_research.xlsx
+++ b/app/reports/FLR_research.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -151,8 +151,6 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -595,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -620,7 +618,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-04 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-06 04:16 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +638,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.832</v>
+        <v>0.738</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -656,7 +654,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -689,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>50.15</v>
+        <v>47.56</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,71 +728,56 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.695</v>
+        <v>0.738</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>comps_percentile</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Peer-relative ranking of P/E, EV/EBITDA, EV/Rev</t>
-        </is>
-      </c>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Honest caveats (read before acting)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Honest caveats (read before acting)</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
+          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
+          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
+          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
+          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>This is a SIGNAL screen, not an investment thesis. Verify with primary filings before acting.</t>
         </is>
@@ -805,7 +788,6 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A1:C2"/>
-    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
@@ -813,6 +795,7 @@
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -879,7 +862,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04470999717712403</v>
+        <v>0.0453600025177002</v>
       </c>
     </row>
     <row r="6">
@@ -899,7 +882,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>1.333</v>
+        <v>1.259</v>
       </c>
     </row>
     <row r="8">
@@ -1208,7 +1191,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>139669893.998006</v>
+        <v>139669896.7199327</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1212,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>50.15</v>
+        <v>47.56</v>
       </c>
     </row>
     <row r="38">
@@ -1434,7 +1417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1508,254 +1491,68 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>7004445184</v>
+        <v>6642700288</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>22.9</v>
+        <v>21.72</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>-12.7</v>
+        <v>-11.67</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ACM</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AECOM</t>
-        </is>
-      </c>
-      <c r="C6" s="32" t="n">
-        <v>9279354880</v>
-      </c>
-      <c r="D6" s="33" t="n">
-        <v>15.073069</v>
-      </c>
-      <c r="E6" s="33" t="n">
-        <v>9.252000000000001</v>
-      </c>
-      <c r="F6" s="33" t="n">
-        <v>0.739</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BLD</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>TopBuild Corp.</t>
-        </is>
-      </c>
-      <c r="C7" s="32" t="n">
-        <v>11476227072</v>
-      </c>
-      <c r="D7" s="33" t="n">
-        <v>22.946539</v>
-      </c>
-      <c r="E7" s="33" t="n">
-        <v>14.027</v>
-      </c>
-      <c r="F7" s="33" t="n">
-        <v>2.545</v>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Peer median</t>
+        </is>
+      </c>
+      <c r="D7" s="32">
+        <f>MEDIAN(D6:D5)</f>
+        <v/>
+      </c>
+      <c r="E7" s="32">
+        <f>MEDIAN(E6:E5)</f>
+        <v/>
+      </c>
+      <c r="F7" s="32">
+        <f>MEDIAN(F6:F5)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>EME</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>EMCOR Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C8" s="32" t="n">
-        <v>37392662528</v>
-      </c>
-      <c r="D8" s="33" t="n">
-        <v>28.176846</v>
-      </c>
-      <c r="E8" s="33" t="n">
-        <v>19.943</v>
-      </c>
-      <c r="F8" s="33" t="n">
-        <v>2.08</v>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Peer mean</t>
+        </is>
+      </c>
+      <c r="D8" s="32">
+        <f>AVERAGE(D6:D5)</f>
+        <v/>
+      </c>
+      <c r="E8" s="32">
+        <f>AVERAGE(E6:E5)</f>
+        <v/>
+      </c>
+      <c r="F8" s="32">
+        <f>AVERAGE(F6:F5)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GLDD</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>GLDD</t>
-        </is>
-      </c>
-      <c r="C9" s="32" t="n"/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Target percentile vs peers</t>
+        </is>
+      </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n"/>
       <c r="F9" s="33" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>GVA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Granite Construction Incorporat</t>
-        </is>
-      </c>
-      <c r="C10" s="32" t="n">
-        <v>6179658752</v>
-      </c>
-      <c r="D10" s="33" t="n">
-        <v>38.49046</v>
-      </c>
-      <c r="E10" s="33" t="n">
-        <v>15.581</v>
-      </c>
-      <c r="F10" s="33" t="n">
-        <v>1.528</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Jacobs Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="C11" s="32" t="n">
-        <v>14564094976</v>
-      </c>
-      <c r="D11" s="33" t="n">
-        <v>36.27647</v>
-      </c>
-      <c r="E11" s="33" t="n">
-        <v>17.071</v>
-      </c>
-      <c r="F11" s="33" t="n">
-        <v>1.328</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>KBR</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>KBR, Inc.</t>
-        </is>
-      </c>
-      <c r="C12" s="32" t="n">
-        <v>4566974464</v>
-      </c>
-      <c r="D12" s="33" t="n">
-        <v>10.625368</v>
-      </c>
-      <c r="E12" s="33" t="n">
-        <v>10.633</v>
-      </c>
-      <c r="F12" s="33" t="n">
-        <v>0.904</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MTRX</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Matrix Service Company</t>
-        </is>
-      </c>
-      <c r="C13" s="32" t="n">
-        <v>390779200</v>
-      </c>
-      <c r="D13" s="33" t="n"/>
-      <c r="E13" s="33" t="n">
-        <v>-70.47</v>
-      </c>
-      <c r="F13" s="33" t="n">
-        <v>0.206</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Peer median</t>
-        </is>
-      </c>
-      <c r="D15" s="34">
-        <f>MEDIAN(D6:D13)</f>
-        <v/>
-      </c>
-      <c r="E15" s="34">
-        <f>MEDIAN(E6:E13)</f>
-        <v/>
-      </c>
-      <c r="F15" s="34">
-        <f>MEDIAN(F6:F13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Peer mean</t>
-        </is>
-      </c>
-      <c r="D16" s="34">
-        <f>AVERAGE(D6:D13)</f>
-        <v/>
-      </c>
-      <c r="E16" s="34">
-        <f>AVERAGE(E6:E13)</f>
-        <v/>
-      </c>
-      <c r="F16" s="34">
-        <f>AVERAGE(F6:F13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Target percentile vs peers</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>(higher pct = more expensive than peers)</t>
         </is>

--- a/app/reports/FLR_research.xlsx
+++ b/app/reports/FLR_research.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -151,6 +151,8 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -593,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -618,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-06 04:16 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-06 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -638,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.738</v>
+        <v>0.846</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -654,7 +656,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -732,52 +734,67 @@
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>comps_percentile</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Peer-relative ranking of P/E, EV/EBITDA, EV/Rev</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Honest caveats (read before acting)</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
-        </is>
-      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
+          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
+          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
+          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>This is a SIGNAL screen, not an investment thesis. Verify with primary filings before acting.</t>
         </is>
@@ -788,6 +805,7 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A1:C2"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
@@ -795,7 +813,6 @@
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -862,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.0453600025177002</v>
+        <v>0.04535999774932861</v>
       </c>
     </row>
     <row r="6">
@@ -1417,7 +1434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1503,56 +1520,242 @@
         <v>0.27</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ACM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AECOM</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="n">
+        <v>9143120896</v>
+      </c>
+      <c r="D6" s="33" t="n">
+        <v>14.851774</v>
+      </c>
+      <c r="E6" s="33" t="n">
+        <v>9.124000000000001</v>
+      </c>
+      <c r="F6" s="33" t="n">
+        <v>0.729</v>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Peer median</t>
-        </is>
-      </c>
-      <c r="D7" s="32">
-        <f>MEDIAN(D6:D5)</f>
-        <v/>
-      </c>
-      <c r="E7" s="32">
-        <f>MEDIAN(E6:E5)</f>
-        <v/>
-      </c>
-      <c r="F7" s="32">
-        <f>MEDIAN(F6:F5)</f>
-        <v/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BLD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TopBuild Corp.</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="n">
+        <v>11309047808</v>
+      </c>
+      <c r="D7" s="33" t="n">
+        <v>22.625</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>13.843</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>2.512</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Peer mean</t>
-        </is>
-      </c>
-      <c r="D8" s="32">
-        <f>AVERAGE(D6:D5)</f>
-        <v/>
-      </c>
-      <c r="E8" s="32">
-        <f>AVERAGE(E6:E5)</f>
-        <v/>
-      </c>
-      <c r="F8" s="32">
-        <f>AVERAGE(F6:F5)</f>
-        <v/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EME</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>EMCOR Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="n">
+        <v>36402704384</v>
+      </c>
+      <c r="D8" s="33" t="n">
+        <v>27.476974</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <v>19.412</v>
+      </c>
+      <c r="F8" s="33" t="n">
+        <v>2.024</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Target percentile vs peers</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GLDD</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GLDD</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="n"/>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n"/>
       <c r="F9" s="33" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GVA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Granite Construction Incorporat</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n">
+        <v>6183596544</v>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>38.410328</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <v>15.804</v>
+      </c>
+      <c r="F10" s="33" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Jacobs Solutions Inc.</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n">
+        <v>14470812672</v>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>36.150444</v>
+      </c>
+      <c r="E11" s="33" t="n">
+        <v>17.218</v>
+      </c>
+      <c r="F11" s="33" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KBR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KBR, Inc.</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n">
+        <v>4508651008</v>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>10.4896755</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F12" s="33" t="n">
+        <v>0.901</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MTRX</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Matrix Service Company</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n">
+        <v>381495008</v>
+      </c>
+      <c r="D13" s="33" t="n"/>
+      <c r="E13" s="33" t="n">
+        <v>-67.625</v>
+      </c>
+      <c r="F13" s="33" t="n">
+        <v>0.198</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Peer median</t>
+        </is>
+      </c>
+      <c r="D15" s="34">
+        <f>MEDIAN(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E15" s="34">
+        <f>MEDIAN(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F15" s="34">
+        <f>MEDIAN(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Peer mean</t>
+        </is>
+      </c>
+      <c r="D16" s="34">
+        <f>AVERAGE(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E16" s="34">
+        <f>AVERAGE(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F16" s="34">
+        <f>AVERAGE(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Target percentile vs peers</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>(higher pct = more expensive than peers)</t>
         </is>

--- a/app/reports/FLR_research.xlsx
+++ b/app/reports/FLR_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-06 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-07 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/FLR_research.xlsx
+++ b/app/reports/FLR_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-07 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-08 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.846</v>
+        <v>0.837</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>47.56</v>
+        <v>49.185</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.738</v>
+        <v>0.711</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04535999774932861</v>
+        <v>0.04552000045776367</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>139669896.7199327</v>
+        <v>139669894.154722</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>47.56</v>
+        <v>49.185</v>
       </c>
     </row>
     <row r="38">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>6642700288</v>
+        <v>6869663744</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>21.72</v>
+        <v>22.46</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>-11.67</v>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>9143120896</v>
+        <v>9087920128</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>14.851774</v>
+        <v>14.762109</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>9.124000000000001</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>11309047808</v>
+        <v>11231931392</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>22.625</v>
+        <v>22.47072</v>
       </c>
       <c r="E7" s="33" t="n">
         <v>13.843</v>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>36402704384</v>
+        <v>36146638848</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>27.476974</v>
+        <v>27.283697</v>
       </c>
       <c r="E8" s="33" t="n">
         <v>19.412</v>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>6183596544</v>
+        <v>6102227456</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>38.410328</v>
+        <v>37.904892</v>
       </c>
       <c r="E10" s="33" t="n">
         <v>15.804</v>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>14470812672</v>
+        <v>14286015488</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>36.150444</v>
+        <v>35.68879</v>
       </c>
       <c r="E11" s="33" t="n">
         <v>17.218</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>4508651008</v>
+        <v>4443987968</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>10.4896755</v>
+        <v>10.339232</v>
       </c>
       <c r="E12" s="33" t="n">
         <v>10.6</v>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>381495008</v>
+        <v>378822304</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">

--- a/app/reports/FLR_research.xlsx
+++ b/app/reports/FLR_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-08 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-09 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.837</v>
+        <v>0.84</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>49.185</v>
+        <v>48.7</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.711</v>
+        <v>0.719</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04552000045776367</v>
+        <v>0.04532000064849853</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>139669894.154722</v>
+        <v>139669888.788501</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>49.185</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>6869663744</v>
+        <v>6801923584</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>22.46</v>
+        <v>22.24</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>-11.67</v>
+        <v>-12.45</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>9087920128</v>
+        <v>9062151168</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>14.762109</v>
+        <v>14.720251</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>9.124000000000001</v>
+        <v>9.095000000000001</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.729</v>
+        <v>0.727</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>11231931392</v>
+        <v>11504933888</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>22.47072</v>
+        <v>22.96517</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>13.843</v>
+        <v>13.767</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>2.512</v>
+        <v>2.498</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>36146638848</v>
+        <v>36384886784</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>27.283697</v>
+        <v>27.472763</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>19.412</v>
+        <v>19.564</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.024</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="9">
@@ -1620,16 +1620,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>6102227456</v>
+        <v>6079478784</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>37.904892</v>
+        <v>37.969944</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>15.804</v>
+        <v>15.66</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>1.55</v>
+        <v>1.536</v>
       </c>
     </row>
     <row r="11">
@@ -1644,16 +1644,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>14286015488</v>
+        <v>14375165952</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>35.68879</v>
+        <v>35.911503</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>17.218</v>
+        <v>16.919</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.34</v>
+        <v>1.316</v>
       </c>
     </row>
     <row r="12">
@@ -1668,16 +1668,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>4443987968</v>
+        <v>4465542656</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>10.339232</v>
+        <v>10.38938</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>10.6</v>
+        <v>10.533</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.901</v>
+        <v>0.896</v>
       </c>
     </row>
     <row r="13">
@@ -1692,14 +1692,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>378822304</v>
+        <v>371648160</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-67.625</v>
+        <v>-68.877</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.198</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/FLR_research.xlsx
+++ b/app/reports/FLR_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-09 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-10 17:40 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.84</v>
+        <v>0.844</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>48.7</v>
+        <v>47.95</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.719</v>
+        <v>0.732</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04532000064849853</v>
+        <v>0.04547999858856201</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>139669888.788501</v>
+        <v>139669894.8070907</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>48.7</v>
+        <v>47.95</v>
       </c>
     </row>
     <row r="38">
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>6801923584</v>
+        <v>6697171456</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>22.24</v>
+        <v>21.89</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>-12.45</v>
+        <v>-12.43</v>
       </c>
       <c r="F5" s="31" t="n">
         <v>0.29</v>
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>9062151168</v>
+        <v>8950323200</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>14.720251</v>
+        <v>14.538602</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>9.095000000000001</v>
+        <v>9.138999999999999</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.727</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="7">
@@ -1556,16 +1556,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>11504933888</v>
+        <v>11075025920</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>22.96517</v>
+        <v>22.119448</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>13.767</v>
+        <v>14.041</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>2.498</v>
+        <v>2.548</v>
       </c>
     </row>
     <row r="8">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>36384886784</v>
+        <v>35002597376</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>27.472763</v>
+        <v>26.37584</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>19.564</v>
+        <v>19.66</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="9">
@@ -1620,16 +1620,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>6079478784</v>
+        <v>6020858368</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>37.969944</v>
+        <v>37.50136</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>15.66</v>
+        <v>15.679</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>1.536</v>
+        <v>1.538</v>
       </c>
     </row>
     <row r="11">
@@ -1644,16 +1644,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>14375165952</v>
+        <v>14753025024</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>35.911503</v>
+        <v>36.855457</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>16.919</v>
+        <v>17.551</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.316</v>
+        <v>1.365</v>
       </c>
     </row>
     <row r="12">
@@ -1668,16 +1668,16 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>4465542656</v>
+        <v>4380593152</v>
       </c>
       <c r="D12" s="33" t="n">
-        <v>10.38938</v>
+        <v>10.19174</v>
       </c>
       <c r="E12" s="33" t="n">
-        <v>10.533</v>
+        <v>10.554</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.896</v>
+        <v>0.897</v>
       </c>
     </row>
     <row r="13">
@@ -1692,14 +1692,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>371648160</v>
+        <v>367709408</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-68.877</v>
+        <v>-64.55200000000001</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.201</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="15">
